--- a/Produccion Astroflores BL25-26-27-28 a la Semana 09.xlsx
+++ b/Produccion Astroflores BL25-26-27-28 a la Semana 09.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView xWindow="-435" yWindow="-60" windowWidth="7290" windowHeight="7410"/>
@@ -12,7 +12,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Astroflores!$A$1:$P$513</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="125725"/>
   <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -547,7 +547,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -564,16 +564,15 @@
     <col min="3" max="3" width="12" style="2" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="13.125" style="2" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="9.375" style="2" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.625" style="2" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="14.625" style="2" customWidth="1"/>
     <col min="8" max="8" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="2" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="13.125" style="2" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" style="2" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.125" style="2" hidden="1" customWidth="1"/>
-    <col min="13" max="15" width="7.875" style="2" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="8.625" style="2" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="0" style="2" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.125" style="2" customWidth="1"/>
+    <col min="13" max="15" width="7.875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="8.625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="11.375" style="2" customWidth="1"/>
     <col min="18" max="16384" width="11.375" style="2"/>
   </cols>
   <sheetData>

--- a/Produccion Astroflores BL25-26-27-28 a la Semana 09.xlsx
+++ b/Produccion Astroflores BL25-26-27-28 a la Semana 09.xlsx
@@ -547,7 +547,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -561,9 +561,9 @@
   <cols>
     <col min="1" max="1" width="7.75" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" style="2" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" style="2" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="9.375" style="2" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.375" style="2" customWidth="1"/>
     <col min="6" max="7" width="14.625" style="2" customWidth="1"/>
     <col min="8" max="8" width="13" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" style="2" customWidth="1"/>

--- a/Produccion Astroflores BL25-26-27-28 a la Semana 09.xlsx
+++ b/Produccion Astroflores BL25-26-27-28 a la Semana 09.xlsx
@@ -547,7 +547,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
